--- a/Self-Service Page Concept .xlsx
+++ b/Self-Service Page Concept .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://4iappssolutions-my.sharepoint.com/personal/narendar_v_4iapps_com/Documents/EBS-Git/4i-Oracle-EBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B1EA9D6-DFD8-466F-B149-12F8B8CBF4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="254" documentId="8_{1B1EA9D6-DFD8-466F-B149-12F8B8CBF4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66DA04F2-457D-497A-BE3D-59A309EEDE9D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{824F18A6-EEF1-436A-AD43-7375EF151B0C}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
   <si>
     <t>Self-Service Request Page</t>
   </si>
@@ -73,36 +73,9 @@
     <t>LOV</t>
   </si>
   <si>
-    <t>Leave Type</t>
-  </si>
-  <si>
-    <t>char</t>
-  </si>
-  <si>
-    <t>xxleave_types</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>S.no</t>
   </si>
   <si>
-    <t>Leave Request</t>
-  </si>
-  <si>
-    <t>Employee Leave Request</t>
-  </si>
-  <si>
-    <t>ELR</t>
-  </si>
-  <si>
-    <t>xxprc</t>
-  </si>
-  <si>
-    <t>xxit</t>
-  </si>
-  <si>
     <t>Request Type Definition</t>
   </si>
   <si>
@@ -121,13 +94,73 @@
     <t>Approved By</t>
   </si>
   <si>
-    <t>xx-xx-xxxx</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>user1</t>
+    <t>Employee Name</t>
+  </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t>&lt;Request Name&gt;</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Raised By</t>
+  </si>
+  <si>
+    <t>Workflow Status</t>
+  </si>
+  <si>
+    <t>Details</t>
+  </si>
+  <si>
+    <t>Heading 1</t>
+  </si>
+  <si>
+    <t>Heading 2</t>
+  </si>
+  <si>
+    <t>Heading 3</t>
+  </si>
+  <si>
+    <t>Heading 4</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>Approval History</t>
+  </si>
+  <si>
+    <t>S.No</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Submission Date</t>
+  </si>
+  <si>
+    <t>Action Date</t>
+  </si>
+  <si>
+    <t>Field Dynamically Changes</t>
+  </si>
+  <si>
+    <t>Request Number</t>
+  </si>
+  <si>
+    <t>Request Name</t>
   </si>
 </sst>
 </file>
@@ -159,7 +192,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -247,55 +280,101 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -317,16 +396,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>730250</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>654050</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -341,8 +420,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5956300" y="1568450"/>
-          <a:ext cx="825500" cy="184150"/>
+          <a:off x="5695950" y="1612900"/>
+          <a:ext cx="1460500" cy="184150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -383,16 +462,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>749300</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>774700</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -407,8 +486,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4673600" y="736600"/>
-          <a:ext cx="825500" cy="184150"/>
+          <a:off x="8458200" y="717550"/>
+          <a:ext cx="1104900" cy="184150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -443,6 +522,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -762,146 +845,132 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB2B6C5-98ED-46FB-81CD-3E40C1C0BD71}">
-  <dimension ref="B2:G13"/>
+  <dimension ref="B2:G14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" customWidth="1"/>
+    <col min="4" max="4" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B4" s="20" t="s">
-        <v>21</v>
+      <c r="B4" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="3"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="3"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="15" t="s">
+      <c r="C6" s="14"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="3"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="16" t="s">
+      <c r="C7" s="14"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="3"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="15" t="s">
+      <c r="C8" s="14"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="3"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B9" s="14"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="3"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="3"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B11" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="18" t="s">
+      <c r="B11" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="3"/>
+      <c r="G11" s="15"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B12" s="10">
-        <v>1</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="3"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="7"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B13" s="6"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -912,134 +981,483 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F72857DB-1139-4BF1-84DD-B459949DF910}">
-  <dimension ref="B2:G13"/>
+  <dimension ref="B2:I18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.90625" customWidth="1"/>
-    <col min="3" max="3" width="13.6328125" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="22.26953125" customWidth="1"/>
+    <col min="5" max="5" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B2" s="15" t="s">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B4" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B6" s="17" t="s">
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B6" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B7" s="10">
-        <v>1</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B8" s="14"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B9" s="23"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
+      <c r="H6" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B9" s="11"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CCEB162-4FB2-4DC7-B379-0B52B43FDB85}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:I29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B2" s="9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B5" s="3"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="14"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="2:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="3"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="14"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" spans="2:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="3"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="2:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="2:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="2:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="3"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="17"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="2:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="3"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="16"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="2:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="3"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="16"/>
+      <c r="I19" s="4"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="17"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="4"/>
+    </row>
+    <row r="21" spans="2:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="3"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="4"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B23" s="5"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="7"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B25" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B26" s="3"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="4"/>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B27" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H27" s="16"/>
+      <c r="I27" s="4"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="4"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B29" s="5"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="7"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Self-Service Page Concept .xlsx
+++ b/Self-Service Page Concept .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://4iappssolutions-my.sharepoint.com/personal/narendar_v_4iapps_com/Documents/EBS-Git/4i-Oracle-EBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="254" documentId="8_{1B1EA9D6-DFD8-466F-B149-12F8B8CBF4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66DA04F2-457D-497A-BE3D-59A309EEDE9D}"/>
+  <xr:revisionPtr revIDLastSave="255" documentId="8_{1B1EA9D6-DFD8-466F-B149-12F8B8CBF4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35DDCCAF-7E6B-4D79-9B95-CDAFBB82A55B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{824F18A6-EEF1-436A-AD43-7375EF151B0C}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>Self-Service Request Page</t>
   </si>
@@ -161,13 +161,16 @@
   </si>
   <si>
     <t>Request Name</t>
+  </si>
+  <si>
+    <t>\\</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,6 +182,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -322,10 +333,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -344,16 +356,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -364,8 +374,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -375,8 +383,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -522,10 +532,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -872,43 +878,36 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B5" s="3"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="14"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="27" t="s">
+      <c r="E6" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="14"/>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="14"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="27" t="s">
+      <c r="E7" t="s">
         <v>6</v>
       </c>
       <c r="F7" s="14"/>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="14"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="27" t="s">
+      <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" s="14"/>
@@ -916,52 +915,41 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="8"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
+      <c r="D9" s="9"/>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="3"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="30" t="s">
+      <c r="F11" s="26" t="s">
         <v>9</v>
       </c>
       <c r="G11" s="15"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="29"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="25"/>
       <c r="F12" s="13"/>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="3"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
       <c r="G13" s="4"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
@@ -1004,8 +992,8 @@
       <c r="B4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -1014,53 +1002,51 @@
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" s="3"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
       <c r="I5" s="4"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="I6" s="21" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="14"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
-      <c r="G8" s="25"/>
+      <c r="G8" s="23"/>
       <c r="H8" s="14"/>
       <c r="I8" s="14"/>
     </row>
@@ -1079,90 +1065,59 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-    </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
+      <c r="D12" s="27" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D12" r:id="rId1" xr:uid="{507D5FBE-84F0-4603-824C-70784416A6C9}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1199,12 +1154,6 @@
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" s="3"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
       <c r="I5" s="4"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.35">
@@ -1212,23 +1161,15 @@
         <v>21</v>
       </c>
       <c r="C6" s="14"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16" t="s">
+      <c r="E6" t="s">
         <v>23</v>
       </c>
       <c r="F6" s="14"/>
-      <c r="G6" s="16"/>
       <c r="H6" s="14"/>
       <c r="I6" s="4"/>
     </row>
     <row r="7" spans="2:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="3"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
@@ -1236,23 +1177,14 @@
         <v>22</v>
       </c>
       <c r="C8" s="14"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16" t="s">
+      <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="14"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="2:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="3"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
@@ -1260,11 +1192,6 @@
         <v>24</v>
       </c>
       <c r="C10" s="14"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.35">
@@ -1293,93 +1220,63 @@
     </row>
     <row r="15" spans="2:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="3"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="17"/>
+      <c r="C16" s="16"/>
       <c r="D16" s="15"/>
-      <c r="E16" s="16"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="2:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="3"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
       <c r="F17" s="4"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="18" t="s">
+      <c r="C18" s="16"/>
+      <c r="D18" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="16"/>
       <c r="F18" s="4"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="16" t="s">
+      <c r="H18" t="s">
         <v>38</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="2:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="3"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
       <c r="F19" s="4"/>
-      <c r="G19" s="16"/>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="17"/>
+      <c r="C20" s="16"/>
       <c r="D20" s="15"/>
-      <c r="E20" s="16"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="2:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="3"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="17"/>
+      <c r="C22" s="16"/>
       <c r="D22" s="15"/>
-      <c r="E22" s="16"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.35">
@@ -1406,12 +1303,6 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B26" s="3"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.35">
@@ -1433,7 +1324,6 @@
       <c r="G27" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="H27" s="16"/>
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.35">
@@ -1443,7 +1333,6 @@
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
       <c r="G28" s="14"/>
-      <c r="H28" s="16"/>
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.35">
